--- a/dashboard-ui/src/components/Research/variables/Variable Definitions RQ134_PH2_April.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions RQ134_PH2_April.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\darren.gemoets_cn\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A07F80-D1E1-4B50-99AA-755461E6F9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="64">
   <si>
     <t>Variables</t>
   </si>
@@ -172,84 +181,6 @@
     <t>1 - 14</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>AF-PS; MF-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>PS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">; MF; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>AF</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">(E.g., Mistral, DeepSeek, Llama) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Leave blank for Oracle trials </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Aligned, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Oracle,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> Baseline, or Comparison (Denotes the page where the participant made forced choices between previous ADMs)</t>
-    </r>
-  </si>
-  <si>
     <t>Target 1-8 for single; Target1-8-Target1-8 for multi (e.g., 3-6 or 8-4)</t>
   </si>
   <si>
@@ -272,40 +203,31 @@
   </si>
   <si>
     <t>0, 25, 50, 75, 100</t>
+  </si>
+  <si>
+    <t>AF-PS; MF-PS; MF; AF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(E.g., Mistral, DeepSeek, Llama) Leave blank for Oracle trials </t>
+  </si>
+  <si>
+    <t>Aligned, Oracle, Baseline, or Comparison (Denotes the page where the participant made forced choices between previous ADMs)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -347,28 +269,16 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -378,25 +288,85 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ffff0000"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office Theme">
       <a:dk1>
@@ -522,7 +492,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
+            <a:outerShdw blurRad="38100" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -531,7 +501,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
+            <a:outerShdw blurRad="38100" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -540,7 +510,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
+            <a:outerShdw blurRad="38100" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -614,7 +584,7 @@
           <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
+          <a:outerShdw blurRad="38100" dist="23000" dir="5400000" rotWithShape="0">
             <a:srgbClr val="000000">
               <a:alpha val="35000"/>
             </a:srgbClr>
@@ -622,7 +592,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -640,7 +610,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -669,7 +639,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -694,7 +664,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -719,7 +689,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -744,7 +714,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -769,7 +739,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -794,7 +764,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -819,7 +789,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -844,7 +814,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -869,7 +839,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -882,9 +852,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -899,7 +875,7 @@
           <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
+          <a:outerShdw blurRad="38100" dist="23000" dir="5400000" rotWithShape="0">
             <a:srgbClr val="000000">
               <a:alpha val="38000"/>
             </a:srgbClr>
@@ -907,7 +883,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -925,7 +901,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -950,7 +926,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -975,7 +951,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1000,7 +976,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1025,7 +1001,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1050,7 +1026,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1075,7 +1051,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1100,7 +1076,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1125,7 +1101,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1150,7 +1126,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1163,9 +1139,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1179,7 +1161,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1197,7 +1179,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1226,7 +1208,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1251,7 +1233,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1276,7 +1258,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1301,7 +1283,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1326,7 +1308,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1351,7 +1333,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1376,7 +1358,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1401,7 +1383,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1426,7 +1408,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1439,350 +1421,360 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z4"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.3516" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.3516" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.3516" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.6719" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.8516" style="1" customWidth="1"/>
-    <col min="10" max="10" width="18.6719" style="1" customWidth="1"/>
-    <col min="11" max="11" width="28.3516" style="1" customWidth="1"/>
-    <col min="12" max="12" width="32.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="27" style="1" customWidth="1"/>
-    <col min="14" max="14" width="47.6719" style="1" customWidth="1"/>
-    <col min="15" max="15" width="22.5" style="1" customWidth="1"/>
-    <col min="16" max="16" width="48.8516" style="1" customWidth="1"/>
-    <col min="17" max="17" width="23.5" style="1" customWidth="1"/>
-    <col min="18" max="18" width="19.3516" style="1" customWidth="1"/>
-    <col min="19" max="19" width="18.6719" style="1" customWidth="1"/>
-    <col min="20" max="22" width="17.6719" style="1" customWidth="1"/>
-    <col min="23" max="26" width="24" style="1" customWidth="1"/>
-    <col min="27" max="16384" width="8.85156" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="30.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="47" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.42578125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="48.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="17.7109375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.85546875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="109.05" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:26" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="2">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="2">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="2">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="2">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="2">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="2">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="2">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="2">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s" s="2">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s" s="2">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s" s="2">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s" s="2">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s" s="2">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s" s="2">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s" s="2">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s" s="3">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s" s="3">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s" s="3">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s" s="3">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s" s="3">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s" s="3">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s" s="3">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s" s="3">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s" s="3">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" ht="153.65" customHeight="1">
-      <c r="A2" t="s" s="2">
+    <row r="2" spans="1:26" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="B2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s" s="2">
+      <c r="C2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D2" t="s" s="2">
+      <c r="D2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E2" t="s" s="2">
+      <c r="E2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s" s="2">
+      <c r="F2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" t="s" s="2">
+      <c r="G2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H2" t="s" s="2">
+      <c r="H2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I2" t="s" s="2">
+      <c r="I2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J2" t="s" s="2">
+      <c r="J2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" t="s" s="2">
+      <c r="K2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="L2" t="s" s="2">
+      <c r="L2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M2" t="s" s="2">
+      <c r="M2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="N2" t="s" s="2">
+      <c r="N2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="O2" t="s" s="2">
+      <c r="O2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P2" t="s" s="2">
+      <c r="P2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" t="s" s="2">
+      <c r="Q2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="R2" t="s" s="2">
+      <c r="R2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="S2" t="s" s="2">
+      <c r="S2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="T2" t="s" s="2">
+      <c r="T2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="U2" t="s" s="3">
+      <c r="U2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="V2" t="s" s="3">
+      <c r="V2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="W2" t="s" s="2">
+      <c r="W2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="X2" t="s" s="2">
+      <c r="X2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" t="s" s="2">
+      <c r="Y2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Z2" t="s" s="2">
+      <c r="Z2" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" ht="599.85" customHeight="1">
-      <c r="A3" t="s" s="2">
+    <row r="3" spans="1:26" ht="180" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="B3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C3" t="s" s="2">
+      <c r="C3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D3" t="s" s="2">
+      <c r="D3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E3" t="s" s="2">
+      <c r="E3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F3" t="s" s="2">
+      <c r="F3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" t="s" s="2">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="K3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="L3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="M3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="N3" t="s" s="2">
+      <c r="N3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O3" t="s" s="3">
+      <c r="O3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P3" t="s" s="2">
+      <c r="P3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" t="s" s="2">
+      <c r="Q3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="R3" t="s" s="2">
+      <c r="R3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="S3" t="s" s="2">
+      <c r="S3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="T3" t="s" s="2">
+      <c r="T3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="U3" t="s" s="3">
+      <c r="U3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="V3" t="s" s="3">
+      <c r="V3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="W3" t="s" s="5">
+      <c r="W3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="X3" t="s" s="2">
+      <c r="X3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Y3" t="s" s="2">
+      <c r="Y3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Z3" t="s" s="2">
+      <c r="Z3" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" ht="376.75" customHeight="1">
-      <c r="A4" t="s" s="2">
+    <row r="4" spans="1:26" ht="300" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" t="s" s="2">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E4" t="s" s="2">
+      <c r="E4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F4" t="s" s="2">
+      <c r="F4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G4" t="s" s="2">
+      <c r="G4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H4" t="s" s="2">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I4" t="s" s="2">
+      <c r="O4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J4" t="s" s="2">
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" t="s" s="3">
+      <c r="R4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="O4" t="s" s="2">
+      <c r="V4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="P4" s="4"/>
-      <c r="Q4" t="s" s="2">
+      <c r="W4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="R4" t="s" s="2">
+      <c r="X4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S4" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="T4" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="U4" t="s" s="3">
+      <c r="Z4" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="V4" t="s" s="3">
-        <v>61</v>
-      </c>
-      <c r="W4" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="X4" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y4" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="Z4" t="s" s="2">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
